--- a/HEAT_Tables_0517_am.xlsx
+++ b/HEAT_Tables_0517_am.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wrhiza-my.sharepoint.com/personal/cparker_wrhi_ac_za/Documents/Desktop/Heat_Project-1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://witsphr-my.sharepoint.com/personal/craig_parker_witsphr_org/Documents/PHR PC/WRHI Files/Documents/Desktop/Heat_Project-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{174E8CE6-EB2B-48E5-B8A1-EF65EB64FB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CCE5EF3-D91F-455B-B916-9C1893B43A05}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{174E8CE6-EB2B-48E5-B8A1-EF65EB64FB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{205F0F2C-DD79-4357-9F60-7D3D646415CF}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{91FD6BB3-C241-4A4C-A7CD-77275B6BC45F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{91FD6BB3-C241-4A4C-A7CD-77275B6BC45F}"/>
   </bookViews>
   <sheets>
     <sheet name="RP1" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="52">
   <si>
     <t>Stage</t>
   </si>
@@ -226,12 +226,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="14">
@@ -407,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -470,6 +476,8 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -485,6 +493,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -804,14 +816,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2136BA5-E5C5-47AA-8FB2-ABBFBE69B251}">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="45.54296875" customWidth="1"/>
     <col min="15" max="15" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -866,8 +878,11 @@
       <c r="R1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="16" x14ac:dyDescent="0.4">
+      <c r="S1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
@@ -922,8 +937,11 @@
       <c r="R2" s="21">
         <v>37</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S2" s="21">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -978,8 +996,11 @@
       <c r="R3" s="21">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S3" s="21">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1034,8 +1055,11 @@
       <c r="R4" s="21">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S4" s="21">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -1090,8 +1114,11 @@
       <c r="R5" s="21">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S5" s="21">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -1146,8 +1173,11 @@
       <c r="R6" s="21">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S6" s="21">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -1202,8 +1232,11 @@
       <c r="R7" s="21">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S7" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -1258,8 +1291,11 @@
       <c r="R8" s="21">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S8" s="21">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="32" t="s">
         <v>20</v>
       </c>
@@ -1314,8 +1350,11 @@
       <c r="R9" s="21">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+      <c r="S9" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>21</v>
       </c>
@@ -1368,6 +1407,9 @@
         <v>36</v>
       </c>
       <c r="R10" s="21">
+        <v>36</v>
+      </c>
+      <c r="S10" s="21">
         <v>36</v>
       </c>
     </row>
@@ -1379,14 +1421,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1C073F-9039-4462-B525-9698BD783580}">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="42.81640625" customWidth="1"/>
     <col min="2" max="2" width="13.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1432,8 +1474,11 @@
       <c r="O1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="16" x14ac:dyDescent="0.4">
+      <c r="P1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
@@ -1479,8 +1524,11 @@
       <c r="O2" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="P2" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>21</v>
       </c>
@@ -1526,8 +1574,11 @@
       <c r="O3" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P3" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1573,8 +1624,11 @@
       <c r="O4" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P4" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -1620,8 +1674,11 @@
       <c r="O5" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P5" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -1667,8 +1724,11 @@
       <c r="O6" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P6" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -1706,8 +1766,11 @@
       <c r="O7" s="3">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P7" s="41">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -1753,8 +1816,11 @@
       <c r="O8" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P8" s="41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -1798,6 +1864,9 @@
         <v>0</v>
       </c>
       <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="41">
         <v>0</v>
       </c>
     </row>
@@ -1809,7 +1878,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12EEDAFB-5DD9-4712-8169-3CA90A65D01B}">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="41.453125" bestFit="1" customWidth="1"/>
@@ -1819,7 +1888,7 @@
     <col min="10" max="10" width="7.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1865,8 +1934,11 @@
       <c r="O1" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="16" x14ac:dyDescent="0.4">
+      <c r="P1" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
@@ -1912,8 +1984,11 @@
       <c r="O2" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="P2" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>21</v>
       </c>
@@ -1953,8 +2028,11 @@
       <c r="O3" s="5">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P3" s="40">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -2000,8 +2078,11 @@
       <c r="O4" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="P4" s="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -2045,8 +2126,11 @@
       <c r="O5" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P5" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -2092,8 +2176,11 @@
       <c r="O6" s="5">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P6" s="40">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -2139,8 +2226,11 @@
       <c r="O7" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P7" s="40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -2170,8 +2260,11 @@
       <c r="O8" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P8" s="40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -2217,12 +2310,15 @@
       <c r="O9" s="5">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P9" s="40">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="12"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="K13" s="10"/>
     </row>
   </sheetData>

--- a/HEAT_Tables_0517_am.xlsx
+++ b/HEAT_Tables_0517_am.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://witsphr-my.sharepoint.com/personal/craig_parker_witsphr_org/Documents/PHR PC/WRHI Files/Documents/Desktop/Heat_Project-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{174E8CE6-EB2B-48E5-B8A1-EF65EB64FB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{205F0F2C-DD79-4357-9F60-7D3D646415CF}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{174E8CE6-EB2B-48E5-B8A1-EF65EB64FB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28CA528B-740E-4785-A757-FC9A699A0D6F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{91FD6BB3-C241-4A4C-A7CD-77275B6BC45F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{91FD6BB3-C241-4A4C-A7CD-77275B6BC45F}"/>
   </bookViews>
   <sheets>
     <sheet name="RP1" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="48">
   <si>
     <t>Stage</t>
   </si>
@@ -101,9 +101,6 @@
     <t>Data sets in hand</t>
   </si>
   <si>
-    <t>Databases harmonised</t>
-  </si>
-  <si>
     <t>Ineligible/declined participation/data currently unavailable</t>
   </si>
   <si>
@@ -113,42 +110,6 @@
     <t>Study site</t>
   </si>
   <si>
-    <t>1st invite</t>
-  </si>
-  <si>
-    <t>2nd invite</t>
-  </si>
-  <si>
-    <t>3rd or more invite</t>
-  </si>
-  <si>
-    <t>Interested</t>
-  </si>
-  <si>
-    <t>Follow up on interest</t>
-  </si>
-  <si>
-    <t>Study documents received</t>
-  </si>
-  <si>
-    <t>Eligibility confirmed</t>
-  </si>
-  <si>
-    <t>Entering DTA</t>
-  </si>
-  <si>
-    <t>DTA complete</t>
-  </si>
-  <si>
-    <t>Ineligible</t>
-  </si>
-  <si>
-    <t>Declined participation</t>
-  </si>
-  <si>
-    <t>Data unavailable</t>
-  </si>
-  <si>
     <t>Benin</t>
   </si>
   <si>
@@ -195,6 +156,33 @@
   </si>
   <si>
     <t>Zimbabwe</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Botswana</t>
+  </si>
+  <si>
+    <t>DRC</t>
+  </si>
+  <si>
+    <t>Lesotho</t>
+  </si>
+  <si>
+    <t>Mali</t>
+  </si>
+  <si>
+    <t>Mozambique</t>
+  </si>
+  <si>
+    <t>Rwanda</t>
+  </si>
+  <si>
+    <t>Sierra Leone</t>
+  </si>
+  <si>
+    <t>Database harmonization</t>
   </si>
 </sst>
 </file>
@@ -204,7 +192,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yy/mm/dd;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -225,6 +213,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -240,7 +236,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -343,11 +339,11 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -358,30 +354,6 @@
         <color rgb="FF000000"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -389,23 +361,8 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <right/>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -413,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -433,15 +390,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -455,29 +403,21 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -816,42 +756,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2136BA5-E5C5-47AA-8FB2-ABBFBE69B251}">
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="45.54296875" customWidth="1"/>
     <col min="15" max="15" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="16" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="18" t="s">
+    <row r="1" spans="1:20" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="18" t="s">
+      <c r="E1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="17" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -881,9 +821,12 @@
       <c r="S1" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" ht="16" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
+      <c r="T1" s="26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A2" s="32" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="5">
@@ -907,42 +850,45 @@
       <c r="H2" s="5">
         <v>99</v>
       </c>
-      <c r="I2" s="21">
+      <c r="I2" s="18">
         <v>96</v>
       </c>
-      <c r="J2" s="21">
+      <c r="J2" s="18">
         <v>96</v>
       </c>
-      <c r="K2" s="21">
+      <c r="K2" s="18">
         <v>96</v>
       </c>
-      <c r="L2" s="21">
+      <c r="L2" s="18">
         <v>82</v>
       </c>
-      <c r="M2" s="21">
+      <c r="M2" s="18">
         <v>74</v>
       </c>
-      <c r="N2" s="21">
+      <c r="N2" s="18">
         <v>73</v>
       </c>
-      <c r="O2" s="21">
+      <c r="O2" s="18">
         <v>57</v>
       </c>
-      <c r="P2" s="21">
+      <c r="P2" s="18">
         <v>58</v>
       </c>
-      <c r="Q2" s="21">
+      <c r="Q2" s="18">
         <v>58</v>
       </c>
-      <c r="R2" s="21">
+      <c r="R2" s="18">
         <v>37</v>
       </c>
-      <c r="S2" s="21">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+      <c r="S2" s="18">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A3" s="32" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="5">
@@ -966,42 +912,45 @@
       <c r="H3" s="5">
         <v>4</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="18">
         <v>3</v>
       </c>
-      <c r="J3" s="21">
+      <c r="J3" s="18">
         <v>3</v>
       </c>
-      <c r="K3" s="21">
-        <v>1</v>
-      </c>
-      <c r="L3" s="21">
+      <c r="K3" s="18">
+        <v>1</v>
+      </c>
+      <c r="L3" s="18">
         <v>13</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="18">
         <v>19</v>
       </c>
-      <c r="N3" s="21">
+      <c r="N3" s="18">
         <v>15</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="18">
         <v>22</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="18">
         <v>16</v>
       </c>
-      <c r="Q3" s="21">
+      <c r="Q3" s="18">
         <v>12</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="18">
         <v>31</v>
       </c>
-      <c r="S3" s="21">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+      <c r="S3" s="18">
+        <v>46</v>
+      </c>
+      <c r="T3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A4" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="5">
@@ -1025,42 +974,45 @@
       <c r="H4" s="5">
         <v>24</v>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="18">
         <v>18</v>
       </c>
-      <c r="J4" s="21">
+      <c r="J4" s="18">
         <v>15</v>
       </c>
-      <c r="K4" s="21">
+      <c r="K4" s="18">
         <v>15</v>
       </c>
-      <c r="L4" s="21">
+      <c r="L4" s="18">
         <v>15</v>
       </c>
-      <c r="M4" s="21">
+      <c r="M4" s="18">
         <v>17</v>
       </c>
-      <c r="N4" s="21">
+      <c r="N4" s="18">
         <v>18</v>
       </c>
-      <c r="O4" s="21">
+      <c r="O4" s="18">
         <v>19</v>
       </c>
-      <c r="P4" s="21">
+      <c r="P4" s="18">
         <v>23</v>
       </c>
-      <c r="Q4" s="21">
+      <c r="Q4" s="18">
         <v>25</v>
       </c>
-      <c r="R4" s="21">
+      <c r="R4" s="18">
         <v>25</v>
       </c>
-      <c r="S4" s="21">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+      <c r="S4" s="18">
+        <v>33</v>
+      </c>
+      <c r="T4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A5" s="32" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="5">
@@ -1084,42 +1036,45 @@
       <c r="H5" s="5">
         <v>47</v>
       </c>
-      <c r="I5" s="21">
+      <c r="I5" s="18">
         <v>45</v>
       </c>
-      <c r="J5" s="21">
+      <c r="J5" s="18">
         <v>45</v>
       </c>
-      <c r="K5" s="21">
+      <c r="K5" s="18">
         <v>45</v>
       </c>
-      <c r="L5" s="21">
+      <c r="L5" s="18">
         <v>36</v>
       </c>
-      <c r="M5" s="21">
+      <c r="M5" s="18">
         <v>34</v>
       </c>
-      <c r="N5" s="21">
+      <c r="N5" s="18">
         <v>35</v>
       </c>
-      <c r="O5" s="21">
+      <c r="O5" s="18">
         <v>43</v>
       </c>
-      <c r="P5" s="21">
+      <c r="P5" s="18">
         <v>36</v>
       </c>
-      <c r="Q5" s="21">
+      <c r="Q5" s="18">
         <v>38</v>
       </c>
-      <c r="R5" s="21">
+      <c r="R5" s="18">
         <v>40</v>
       </c>
-      <c r="S5" s="21">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+      <c r="S5" s="18">
+        <v>53</v>
+      </c>
+      <c r="T5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A6" s="32" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="5">
@@ -1143,42 +1098,45 @@
       <c r="H6" s="5">
         <v>24</v>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="18">
         <v>21</v>
       </c>
-      <c r="J6" s="21">
+      <c r="J6" s="18">
         <v>24</v>
       </c>
-      <c r="K6" s="21">
+      <c r="K6" s="18">
         <v>26</v>
       </c>
-      <c r="L6" s="21">
+      <c r="L6" s="18">
         <v>26</v>
       </c>
-      <c r="M6" s="21">
+      <c r="M6" s="18">
         <v>26</v>
       </c>
-      <c r="N6" s="21">
+      <c r="N6" s="18">
         <v>28</v>
       </c>
-      <c r="O6" s="21">
+      <c r="O6" s="18">
         <v>24</v>
       </c>
-      <c r="P6" s="21">
+      <c r="P6" s="18">
         <v>31</v>
       </c>
-      <c r="Q6" s="21">
+      <c r="Q6" s="18">
         <v>26</v>
       </c>
-      <c r="R6" s="21">
+      <c r="R6" s="18">
         <v>24</v>
       </c>
-      <c r="S6" s="21">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+      <c r="S6" s="18">
+        <v>21</v>
+      </c>
+      <c r="T6">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A7" s="32" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="5">
@@ -1202,42 +1160,45 @@
       <c r="H7" s="5">
         <v>6</v>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="18">
         <v>7</v>
       </c>
-      <c r="J7" s="21">
+      <c r="J7" s="18">
         <v>7</v>
       </c>
-      <c r="K7" s="21">
+      <c r="K7" s="18">
         <v>5</v>
       </c>
-      <c r="L7" s="21">
+      <c r="L7" s="18">
         <v>6</v>
       </c>
-      <c r="M7" s="21">
+      <c r="M7" s="18">
         <v>5</v>
       </c>
-      <c r="N7" s="21">
+      <c r="N7" s="18">
         <v>5</v>
       </c>
-      <c r="O7" s="21">
-        <v>4</v>
-      </c>
-      <c r="P7" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="21">
-        <v>1</v>
-      </c>
-      <c r="R7" s="21">
-        <v>3</v>
-      </c>
-      <c r="S7" s="21">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+      <c r="O7" s="18">
+        <v>4</v>
+      </c>
+      <c r="P7" s="18">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="18">
+        <v>1</v>
+      </c>
+      <c r="R7" s="18">
+        <v>4</v>
+      </c>
+      <c r="S7" s="18">
+        <v>5</v>
+      </c>
+      <c r="T7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A8" s="32" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="5">
@@ -1261,102 +1222,108 @@
       <c r="H8" s="5">
         <v>7</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="18">
         <v>12</v>
       </c>
-      <c r="J8" s="21">
+      <c r="J8" s="18">
         <v>13</v>
       </c>
-      <c r="K8" s="21">
+      <c r="K8" s="18">
         <v>15</v>
       </c>
-      <c r="L8" s="21">
+      <c r="L8" s="18">
         <v>16</v>
       </c>
-      <c r="M8" s="21">
+      <c r="M8" s="18">
         <v>18</v>
       </c>
-      <c r="N8" s="21">
+      <c r="N8" s="18">
         <v>19</v>
       </c>
-      <c r="O8" s="21">
+      <c r="O8" s="18">
         <v>22</v>
       </c>
-      <c r="P8" s="21">
+      <c r="P8" s="18">
         <v>25</v>
       </c>
-      <c r="Q8" s="21">
+      <c r="Q8" s="18">
         <v>26</v>
       </c>
-      <c r="R8" s="21">
-        <v>26</v>
-      </c>
-      <c r="S8" s="21">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="R8" s="18">
+        <v>25</v>
+      </c>
+      <c r="S8" s="18">
+        <v>25</v>
+      </c>
+      <c r="T8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="18">
+        <v>0</v>
+      </c>
+      <c r="J9" s="18">
+        <v>0</v>
+      </c>
+      <c r="K9" s="18">
+        <v>0</v>
+      </c>
+      <c r="L9" s="18">
+        <v>0</v>
+      </c>
+      <c r="M9" s="18">
+        <v>0</v>
+      </c>
+      <c r="N9" s="18">
+        <v>0</v>
+      </c>
+      <c r="O9" s="18">
+        <v>0</v>
+      </c>
+      <c r="P9" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="18">
+        <v>2</v>
+      </c>
+      <c r="R9" s="18">
+        <v>2</v>
+      </c>
+      <c r="S9" s="18">
+        <v>2</v>
+      </c>
+      <c r="T9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="32" t="s">
         <v>20</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9" s="21">
-        <v>0</v>
-      </c>
-      <c r="J9" s="21">
-        <v>0</v>
-      </c>
-      <c r="K9" s="21">
-        <v>0</v>
-      </c>
-      <c r="L9" s="21">
-        <v>0</v>
-      </c>
-      <c r="M9" s="21">
-        <v>0</v>
-      </c>
-      <c r="N9" s="21">
-        <v>0</v>
-      </c>
-      <c r="O9" s="21">
-        <v>0</v>
-      </c>
-      <c r="P9" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="21">
-        <v>2</v>
-      </c>
-      <c r="R9" s="21">
-        <v>2</v>
-      </c>
-      <c r="S9" s="21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="B10" s="5">
         <v>0</v>
@@ -1379,39 +1346,72 @@
       <c r="H10" s="5">
         <v>11</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="18">
         <v>20</v>
       </c>
-      <c r="J10" s="21">
+      <c r="J10" s="18">
         <v>21</v>
       </c>
-      <c r="K10" s="21">
+      <c r="K10" s="18">
         <v>21</v>
       </c>
-      <c r="L10" s="21">
+      <c r="L10" s="18">
         <v>30</v>
       </c>
-      <c r="M10" s="21">
+      <c r="M10" s="18">
         <v>31</v>
       </c>
-      <c r="N10" s="21">
+      <c r="N10" s="18">
         <v>31</v>
       </c>
-      <c r="O10" s="21">
+      <c r="O10" s="18">
         <v>33</v>
       </c>
-      <c r="P10" s="21">
+      <c r="P10" s="18">
         <v>34</v>
       </c>
-      <c r="Q10" s="21">
+      <c r="Q10" s="18">
         <v>36</v>
       </c>
-      <c r="R10" s="21">
-        <v>36</v>
-      </c>
-      <c r="S10" s="21">
-        <v>36</v>
-      </c>
+      <c r="R10" s="18">
+        <v>34</v>
+      </c>
+      <c r="S10" s="18">
+        <v>37</v>
+      </c>
+      <c r="T10">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A12" s="31"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A13" s="32"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A14" s="32"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A15" s="32"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A16" s="32"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="32"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" s="32"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="32"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="32"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" s="32"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1421,15 +1421,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1C073F-9039-4462-B525-9698BD783580}">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="42.81640625" customWidth="1"/>
     <col min="2" max="2" width="13.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
@@ -1468,7 +1468,7 @@
       <c r="M1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="39" t="s">
+      <c r="N1" s="23" t="s">
         <v>4</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -1477,8 +1477,11 @@
       <c r="P1" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" ht="16" x14ac:dyDescent="0.4">
+      <c r="Q1" s="27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
@@ -1515,7 +1518,7 @@
       <c r="L2" s="5">
         <v>0</v>
       </c>
-      <c r="M2" s="21">
+      <c r="M2" s="18">
         <v>0</v>
       </c>
       <c r="N2" s="7">
@@ -1524,13 +1527,16 @@
       <c r="O2" s="3">
         <v>0</v>
       </c>
-      <c r="P2" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
-        <v>21</v>
+      <c r="P2" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="32" t="s">
+        <v>20</v>
       </c>
       <c r="B3" s="5">
         <v>0</v>
@@ -1544,7 +1550,7 @@
       <c r="E3" s="5">
         <v>0</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="18">
         <v>0</v>
       </c>
       <c r="G3" s="8">
@@ -1565,7 +1571,7 @@
       <c r="L3" s="5">
         <v>0</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="18">
         <v>0</v>
       </c>
       <c r="N3" s="7">
@@ -1574,12 +1580,15 @@
       <c r="O3" s="3">
         <v>0</v>
       </c>
-      <c r="P3" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+      <c r="P3" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="32" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="5">
@@ -1594,7 +1603,7 @@
       <c r="E4" s="5">
         <v>4</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="18">
         <v>2</v>
       </c>
       <c r="G4" s="8">
@@ -1615,7 +1624,7 @@
       <c r="L4" s="5">
         <v>4</v>
       </c>
-      <c r="M4" s="21">
+      <c r="M4" s="18">
         <v>4</v>
       </c>
       <c r="N4" s="7">
@@ -1624,12 +1633,15 @@
       <c r="O4" s="3">
         <v>1</v>
       </c>
-      <c r="P4" s="41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+      <c r="P4" s="25">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A5" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="5">
@@ -1644,7 +1656,7 @@
       <c r="E5" s="5">
         <v>5</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="18">
         <v>6</v>
       </c>
       <c r="G5" s="8">
@@ -1665,7 +1677,7 @@
       <c r="L5" s="5">
         <v>2</v>
       </c>
-      <c r="M5" s="21">
+      <c r="M5" s="18">
         <v>2</v>
       </c>
       <c r="N5" s="7">
@@ -1674,12 +1686,15 @@
       <c r="O5" s="3">
         <v>2</v>
       </c>
-      <c r="P5" s="41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+      <c r="P5" s="25">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A6" s="32" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="5">
@@ -1694,7 +1709,7 @@
       <c r="E6" s="5">
         <v>11</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="18">
         <v>8</v>
       </c>
       <c r="G6" s="8">
@@ -1715,7 +1730,7 @@
       <c r="L6" s="5">
         <v>0</v>
       </c>
-      <c r="M6" s="21">
+      <c r="M6" s="18">
         <v>0</v>
       </c>
       <c r="N6" s="7">
@@ -1724,11 +1739,14 @@
       <c r="O6" s="3">
         <v>0</v>
       </c>
-      <c r="P6" s="41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="P6" s="25">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -1736,7 +1754,7 @@
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="21">
+      <c r="F7" s="18">
         <v>4</v>
       </c>
       <c r="G7" s="8">
@@ -1757,7 +1775,7 @@
       <c r="L7" s="5">
         <v>12</v>
       </c>
-      <c r="M7" s="21">
+      <c r="M7" s="18">
         <v>12</v>
       </c>
       <c r="N7" s="7">
@@ -1766,11 +1784,14 @@
       <c r="O7" s="3">
         <v>15</v>
       </c>
-      <c r="P7" s="41">
+      <c r="P7" s="25">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q7" s="25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -1801,13 +1822,13 @@
       <c r="J8" s="5">
         <v>0</v>
       </c>
-      <c r="K8" s="21">
+      <c r="K8" s="18">
         <v>0</v>
       </c>
       <c r="L8" s="5">
         <v>2</v>
       </c>
-      <c r="M8" s="21">
+      <c r="M8" s="18">
         <v>2</v>
       </c>
       <c r="N8" s="7">
@@ -1816,12 +1837,15 @@
       <c r="O8" s="3">
         <v>2</v>
       </c>
-      <c r="P8" s="41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+      <c r="P8" s="25">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A9" s="32" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="5">
@@ -1836,7 +1860,7 @@
       <c r="E9" s="5">
         <v>0</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="18">
         <v>0</v>
       </c>
       <c r="G9" s="8">
@@ -1857,7 +1881,7 @@
       <c r="L9" s="5">
         <v>0</v>
       </c>
-      <c r="M9" s="21">
+      <c r="M9" s="18">
         <v>0</v>
       </c>
       <c r="N9" s="7">
@@ -1866,9 +1890,47 @@
       <c r="O9" s="3">
         <v>0</v>
       </c>
-      <c r="P9" s="41">
-        <v>0</v>
-      </c>
+      <c r="P9" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A10" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A12" s="31"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A13" s="32"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A14" s="32"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A15" s="32"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A16" s="32"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="32"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" s="32"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="32"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="32"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" s="32"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1878,7 +1940,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12EEDAFB-5DD9-4712-8169-3CA90A65D01B}">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="41.453125" bestFit="1" customWidth="1"/>
@@ -1888,7 +1950,7 @@
     <col min="10" max="10" width="7.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1937,8 +1999,11 @@
       <c r="P1" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" ht="16" x14ac:dyDescent="0.4">
+      <c r="Q1" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
@@ -1954,7 +2019,7 @@
       <c r="E2" s="5">
         <v>0</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="18">
         <v>0</v>
       </c>
       <c r="G2" s="8">
@@ -1984,13 +2049,16 @@
       <c r="O2" s="5">
         <v>0</v>
       </c>
-      <c r="P2" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="P2" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -1998,7 +2066,7 @@
       <c r="E3" s="5">
         <v>5</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="18">
         <v>8</v>
       </c>
       <c r="G3" s="8">
@@ -2028,11 +2096,14 @@
       <c r="O3" s="5">
         <v>8</v>
       </c>
-      <c r="P3" s="40">
+      <c r="P3" s="24">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q3" s="24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -2048,7 +2119,7 @@
       <c r="E4" s="5">
         <v>8</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="18">
         <v>6</v>
       </c>
       <c r="G4" s="8">
@@ -2078,32 +2149,35 @@
       <c r="O4" s="5">
         <v>2</v>
       </c>
-      <c r="P4" s="40">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="P4" s="24">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22">
-        <v>1</v>
-      </c>
-      <c r="E5" s="22">
+      <c r="B5" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19">
+        <v>1</v>
+      </c>
+      <c r="E5" s="19">
         <v>3</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="20">
         <v>3</v>
       </c>
       <c r="G5" s="8">
         <v>3</v>
       </c>
-      <c r="H5" s="24" t="s">
-        <v>22</v>
+      <c r="H5" s="21" t="s">
+        <v>21</v>
       </c>
       <c r="I5" s="8">
         <v>1</v>
@@ -2126,11 +2200,14 @@
       <c r="O5" s="5">
         <v>1</v>
       </c>
-      <c r="P5" s="40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="P5" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -2146,7 +2223,7 @@
       <c r="E6" s="5">
         <v>19</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="18">
         <v>17</v>
       </c>
       <c r="G6" s="8">
@@ -2176,11 +2253,14 @@
       <c r="O6" s="5">
         <v>13</v>
       </c>
-      <c r="P6" s="40">
+      <c r="P6" s="24">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q6" s="24">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -2196,7 +2276,7 @@
       <c r="E7" s="5">
         <v>4</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="18">
         <v>4</v>
       </c>
       <c r="G7" s="8">
@@ -2226,11 +2306,14 @@
       <c r="O7" s="5">
         <v>3</v>
       </c>
-      <c r="P7" s="40">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="P7" s="24">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -2238,7 +2321,7 @@
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="21"/>
+      <c r="F8" s="18"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
@@ -2260,11 +2343,14 @@
       <c r="O8" s="5">
         <v>4</v>
       </c>
-      <c r="P8" s="40">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="P8" s="24">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -2280,7 +2366,7 @@
       <c r="E9" s="5">
         <v>6</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="18">
         <v>7</v>
       </c>
       <c r="G9" s="8">
@@ -2310,15 +2396,44 @@
       <c r="O9" s="5">
         <v>15</v>
       </c>
-      <c r="P9" s="40">
+      <c r="P9" s="24">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A10" s="12"/>
+      <c r="Q9" s="24">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A10" s="12" t="s">
+        <v>47</v>
+      </c>
       <c r="B10" s="12"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="J10" s="29">
+        <v>0</v>
+      </c>
+      <c r="K10" s="29">
+        <v>0</v>
+      </c>
+      <c r="L10" s="28">
+        <v>0</v>
+      </c>
+      <c r="M10" s="28">
+        <v>0</v>
+      </c>
+      <c r="N10" s="28">
+        <v>0</v>
+      </c>
+      <c r="O10" s="28">
+        <v>0</v>
+      </c>
+      <c r="P10" s="30">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="K13" s="10"/>
     </row>
   </sheetData>
@@ -2329,478 +2444,223 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{824D3A57-90AC-4527-870E-30FD69A9F0BB}">
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="64" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A2" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B2" s="14">
+        <v>4</v>
+      </c>
+      <c r="C2" s="10"/>
+    </row>
+    <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A3" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="14">
+        <v>2</v>
+      </c>
+      <c r="C3" s="10"/>
+    </row>
+    <row r="4" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A4" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="B4" s="14">
+        <v>4</v>
+      </c>
+      <c r="C4" s="10"/>
+    </row>
+    <row r="5" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A5" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="B5" s="14">
+        <v>2</v>
+      </c>
+      <c r="C5" s="10"/>
+    </row>
+    <row r="6" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A6" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="B6" s="14">
+        <v>1</v>
+      </c>
+      <c r="C6" s="10"/>
+    </row>
+    <row r="7" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A7" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="14">
+        <v>3</v>
+      </c>
+      <c r="C7" s="10"/>
+    </row>
+    <row r="8" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="B8" s="4">
+        <v>19</v>
+      </c>
+      <c r="C8" s="10"/>
+    </row>
+    <row r="9" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="B9" s="4">
+        <v>1</v>
+      </c>
+      <c r="C9" s="10"/>
+    </row>
+    <row r="10" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="B10" s="4">
+        <v>10</v>
+      </c>
+      <c r="C10" s="10"/>
+    </row>
+    <row r="11" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="B11" s="4">
+        <v>17</v>
+      </c>
+      <c r="C11" s="10"/>
+    </row>
+    <row r="12" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="4">
+        <v>2</v>
+      </c>
+      <c r="C12" s="10"/>
+    </row>
+    <row r="13" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="B13" s="4">
+        <v>19</v>
+      </c>
+      <c r="C13" s="10"/>
+    </row>
+    <row r="14" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="4">
+        <v>2</v>
+      </c>
+      <c r="C14" s="10"/>
+    </row>
+    <row r="15" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A15" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="4">
+        <v>3</v>
+      </c>
+      <c r="C15" s="10"/>
+    </row>
+    <row r="16" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A16" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="B16" s="4">
+        <v>40</v>
+      </c>
+      <c r="C16" s="10"/>
+    </row>
+    <row r="17" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="B17" s="4">
+        <v>9</v>
+      </c>
+      <c r="C17" s="10"/>
+    </row>
+    <row r="18" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="4">
+        <v>2</v>
+      </c>
+      <c r="C18" s="10"/>
+    </row>
+    <row r="19" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="17" t="s">
+      <c r="B19" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A21" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="16" x14ac:dyDescent="0.4">
-      <c r="A2" s="14" t="s">
+      <c r="B21" s="4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A22" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="25">
-        <v>1</v>
-      </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26">
-        <v>1</v>
-      </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="27">
-        <v>1</v>
-      </c>
-      <c r="M2" s="28"/>
-      <c r="N2" s="10"/>
-    </row>
-    <row r="3" spans="1:14" ht="16" x14ac:dyDescent="0.4">
-      <c r="A3" s="14" t="s">
+      <c r="B22" s="22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26">
-        <v>3</v>
-      </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25">
-        <v>1</v>
-      </c>
-      <c r="L3" s="27"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="10"/>
-    </row>
-    <row r="4" spans="1:14" ht="16" x14ac:dyDescent="0.4">
-      <c r="A4" s="14" t="s">
+      <c r="B23" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26">
-        <v>1</v>
-      </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="26">
-        <v>1</v>
-      </c>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="10"/>
-    </row>
-    <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.4">
-      <c r="A5" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="26">
-        <v>1</v>
-      </c>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="10"/>
-    </row>
-    <row r="6" spans="1:14" ht="16" x14ac:dyDescent="0.4">
-      <c r="A6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29">
-        <v>6</v>
-      </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29">
-        <v>5</v>
-      </c>
-      <c r="G6" s="29">
-        <v>1</v>
-      </c>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29">
-        <v>3</v>
-      </c>
-      <c r="J6" s="29">
-        <v>1</v>
-      </c>
-      <c r="K6" s="29"/>
-      <c r="L6" s="21">
-        <v>2</v>
-      </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="10"/>
-    </row>
-    <row r="7" spans="1:14" ht="16" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29">
-        <v>1</v>
-      </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="10"/>
-    </row>
-    <row r="8" spans="1:14" ht="16" x14ac:dyDescent="0.4">
-      <c r="A8" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29">
-        <v>1</v>
-      </c>
-      <c r="D8" s="29">
-        <v>3</v>
-      </c>
-      <c r="E8" s="29">
-        <v>2</v>
-      </c>
-      <c r="F8" s="29">
-        <v>1</v>
-      </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29">
-        <v>2</v>
-      </c>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29">
-        <v>1</v>
-      </c>
-      <c r="L8" s="21"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="10"/>
-    </row>
-    <row r="9" spans="1:14" ht="16" x14ac:dyDescent="0.4">
-      <c r="A9" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="10">
-        <v>2</v>
-      </c>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29">
-        <v>6</v>
-      </c>
-      <c r="J9" s="29">
-        <v>2</v>
-      </c>
-      <c r="K9" s="29">
-        <v>1</v>
-      </c>
-      <c r="L9" s="21">
-        <v>5</v>
-      </c>
-      <c r="M9" s="8">
-        <v>1</v>
-      </c>
-      <c r="N9" s="10"/>
-    </row>
-    <row r="10" spans="1:14" ht="16" x14ac:dyDescent="0.4">
-      <c r="A10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29">
-        <v>1</v>
-      </c>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29">
-        <v>1</v>
-      </c>
-      <c r="I10" s="29">
-        <v>2</v>
-      </c>
-      <c r="J10" s="29">
-        <v>12</v>
-      </c>
-      <c r="K10" s="29">
-        <v>2</v>
-      </c>
-      <c r="L10" s="21">
-        <v>1</v>
-      </c>
-      <c r="M10" s="8"/>
-      <c r="N10" s="10"/>
-    </row>
-    <row r="11" spans="1:14" ht="16" x14ac:dyDescent="0.4">
-      <c r="A11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="29">
-        <v>4</v>
-      </c>
-      <c r="C11" s="29">
-        <v>1</v>
-      </c>
-      <c r="D11" s="29">
-        <v>3</v>
-      </c>
-      <c r="E11" s="29">
-        <v>4</v>
-      </c>
-      <c r="F11" s="29">
-        <v>4</v>
-      </c>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29">
-        <v>1</v>
-      </c>
-      <c r="I11" s="29">
-        <v>1</v>
-      </c>
-      <c r="J11" s="5">
-        <v>4</v>
-      </c>
-      <c r="K11" s="5">
-        <v>3</v>
-      </c>
-      <c r="L11" s="21"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="10"/>
-    </row>
-    <row r="12" spans="1:14" ht="16" x14ac:dyDescent="0.4">
-      <c r="A12" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29">
-        <v>3</v>
-      </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29">
-        <v>1</v>
-      </c>
-      <c r="F12" s="29">
-        <v>2</v>
-      </c>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29">
-        <v>1</v>
-      </c>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="21">
-        <v>1</v>
-      </c>
-      <c r="M12" s="8"/>
-      <c r="N12" s="10"/>
-    </row>
-    <row r="13" spans="1:14" ht="16" x14ac:dyDescent="0.4">
-      <c r="A13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29">
-        <v>1</v>
-      </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="10"/>
-    </row>
-    <row r="14" spans="1:14" ht="16" x14ac:dyDescent="0.4">
-      <c r="A14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="29">
-        <v>1</v>
-      </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29">
-        <v>2</v>
-      </c>
-      <c r="E14" s="29">
-        <v>2</v>
-      </c>
-      <c r="F14" s="29">
-        <v>2</v>
-      </c>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29">
-        <v>4</v>
-      </c>
-      <c r="I14" s="29">
-        <v>4</v>
-      </c>
-      <c r="J14" s="31">
-        <v>12</v>
-      </c>
-      <c r="K14" s="29">
-        <v>2</v>
-      </c>
-      <c r="L14" s="30">
-        <v>2</v>
-      </c>
-      <c r="M14" s="8">
-        <v>1</v>
-      </c>
-      <c r="N14" s="10"/>
-    </row>
-    <row r="15" spans="1:14" ht="16" x14ac:dyDescent="0.4">
-      <c r="A15" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31">
-        <v>3</v>
-      </c>
-      <c r="E15" s="31">
-        <v>4</v>
-      </c>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="34">
-        <v>5</v>
-      </c>
-      <c r="J15" s="35">
-        <v>1</v>
-      </c>
-      <c r="K15" s="36">
-        <v>2</v>
-      </c>
-      <c r="L15" s="37">
-        <v>8</v>
-      </c>
-      <c r="M15" s="38"/>
-      <c r="N15" s="10"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="3">
-        <v>17</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="10"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" s="3">
-        <v>2</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="10"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="N18" s="10"/>
+      <c r="B24" s="3">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M17">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B17">
     <sortCondition ref="A2:A17"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/HEAT_Tables_0517_am.xlsx
+++ b/HEAT_Tables_0517_am.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="82" documentId="8_{174E8CE6-EB2B-48E5-B8A1-EF65EB64FB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28CA528B-740E-4785-A757-FC9A699A0D6F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{91FD6BB3-C241-4A4C-A7CD-77275B6BC45F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{91FD6BB3-C241-4A4C-A7CD-77275B6BC45F}"/>
   </bookViews>
   <sheets>
     <sheet name="RP1" sheetId="3" r:id="rId1"/>
@@ -2664,16 +2664,16 @@
     <sortCondition ref="A2:A17"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="84e45b98-9724-46df-936f-ec42a4cf951b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2930,17 +2930,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="84e45b98-9724-46df-936f-ec42a4cf951b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{402FBE93-6AD6-436A-9711-D8E18344BF8D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29346A3B-E74B-4386-AD79-218823B89808}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="84e45b98-9724-46df-936f-ec42a4cf951b"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2965,11 +2968,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29346A3B-E74B-4386-AD79-218823B89808}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{402FBE93-6AD6-436A-9711-D8E18344BF8D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="84e45b98-9724-46df-936f-ec42a4cf951b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/HEAT_Tables_0517_am.xlsx
+++ b/HEAT_Tables_0517_am.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://witsphr-my.sharepoint.com/personal/craig_parker_witsphr_org/Documents/PHR PC/WRHI Files/Documents/Desktop/Heat_Project-1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CraigParker\OneDrive - Wits PHR\Desktop\Heat_Project-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{174E8CE6-EB2B-48E5-B8A1-EF65EB64FB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28CA528B-740E-4785-A757-FC9A699A0D6F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2629B4B0-F6D2-4533-B601-DE8F7BE2194F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{91FD6BB3-C241-4A4C-A7CD-77275B6BC45F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{91FD6BB3-C241-4A4C-A7CD-77275B6BC45F}"/>
   </bookViews>
   <sheets>
     <sheet name="RP1" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="49">
   <si>
     <t>Stage</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>Database harmonization</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
 </sst>
 </file>
@@ -192,7 +195,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yy/mm/dd;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,6 +224,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -236,7 +246,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -366,11 +376,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -418,6 +437,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -756,14 +777,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2136BA5-E5C5-47AA-8FB2-ABBFBE69B251}">
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="45.54296875" customWidth="1"/>
+    <col min="1" max="1" width="45.453125" customWidth="1"/>
     <col min="15" max="15" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:21" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
@@ -824,8 +845,11 @@
       <c r="T1" s="26" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U1" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" s="32" t="s">
         <v>13</v>
       </c>
@@ -886,8 +910,11 @@
       <c r="T2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U2" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" s="32" t="s">
         <v>14</v>
       </c>
@@ -948,8 +975,11 @@
       <c r="T3">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U3" s="33">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" s="32" t="s">
         <v>15</v>
       </c>
@@ -1010,8 +1040,11 @@
       <c r="T4">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U4" s="33">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" s="32" t="s">
         <v>16</v>
       </c>
@@ -1072,8 +1105,11 @@
       <c r="T5">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U5" s="33">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" s="32" t="s">
         <v>17</v>
       </c>
@@ -1134,8 +1170,11 @@
       <c r="T6">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U6" s="33">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" s="32" t="s">
         <v>18</v>
       </c>
@@ -1196,8 +1235,11 @@
       <c r="T7">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U7" s="33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" s="32" t="s">
         <v>19</v>
       </c>
@@ -1258,8 +1300,11 @@
       <c r="T8">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U8" s="33">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" s="32" t="s">
         <v>47</v>
       </c>
@@ -1320,8 +1365,11 @@
       <c r="T9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+      <c r="U9" s="33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="32" t="s">
         <v>20</v>
       </c>
@@ -1382,20 +1430,23 @@
       <c r="T10">
         <v>41</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U10" s="33">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" s="31"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" s="32"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" s="32"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" s="32"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" s="32"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
@@ -1421,14 +1472,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1C073F-9039-4462-B525-9698BD783580}">
-  <dimension ref="A1:Q21"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:R21"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="42.81640625" customWidth="1"/>
     <col min="2" max="2" width="13.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
@@ -1480,8 +1531,11 @@
       <c r="Q1" s="27" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" ht="16" x14ac:dyDescent="0.4">
+      <c r="R1" s="27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
@@ -1533,8 +1587,11 @@
       <c r="Q2" s="25">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+      <c r="R2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="32" t="s">
         <v>20</v>
       </c>
@@ -1586,8 +1643,11 @@
       <c r="Q3" s="25">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="32" t="s">
         <v>14</v>
       </c>
@@ -1639,8 +1699,11 @@
       <c r="Q4" s="25">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="32" t="s">
         <v>15</v>
       </c>
@@ -1692,8 +1755,11 @@
       <c r="Q5" s="25">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="32" t="s">
         <v>16</v>
       </c>
@@ -1745,8 +1811,11 @@
       <c r="Q6" s="25">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -1790,8 +1859,11 @@
       <c r="Q7" s="25">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -1843,8 +1915,11 @@
       <c r="Q8" s="25">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" s="32" t="s">
         <v>19</v>
       </c>
@@ -1896,25 +1971,28 @@
       <c r="Q9" s="25">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" s="32" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="31"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="32"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" s="32"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" s="32"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" s="32"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
@@ -1940,17 +2018,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12EEDAFB-5DD9-4712-8169-3CA90A65D01B}">
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="41.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="13.7265625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2002,8 +2080,11 @@
       <c r="Q1" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" ht="16" x14ac:dyDescent="0.4">
+      <c r="R1" s="28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
@@ -2055,8 +2136,11 @@
       <c r="Q2" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+      <c r="R2" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>20</v>
       </c>
@@ -2102,8 +2186,11 @@
       <c r="Q3" s="24">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R3" s="28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -2155,8 +2242,11 @@
       <c r="Q4" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="R4" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -2206,8 +2296,11 @@
       <c r="Q5" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R5" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -2259,8 +2352,11 @@
       <c r="Q6" s="24">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R6" s="34">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -2312,8 +2408,11 @@
       <c r="Q7" s="24">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R7" s="34">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -2349,8 +2448,11 @@
       <c r="Q8" s="24">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R8" s="28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -2402,8 +2504,11 @@
       <c r="Q9" s="24">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R9" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>47</v>
       </c>
@@ -2432,8 +2537,11 @@
       <c r="Q10" s="30">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R10" s="28">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="K13" s="10"/>
     </row>
   </sheetData>

--- a/HEAT_Tables_0517_am.xlsx
+++ b/HEAT_Tables_0517_am.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CraigParker\OneDrive - Wits PHR\Desktop\Heat_Project-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2629B4B0-F6D2-4533-B601-DE8F7BE2194F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43ACE461-5900-487E-849B-C1D67B9F504A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{91FD6BB3-C241-4A4C-A7CD-77275B6BC45F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{91FD6BB3-C241-4A4C-A7CD-77275B6BC45F}"/>
   </bookViews>
   <sheets>
     <sheet name="RP1" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="49">
   <si>
     <t>Stage</t>
   </si>
@@ -232,7 +232,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -242,6 +242,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,7 +395,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -439,6 +445,11 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -454,10 +465,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -777,14 +784,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2136BA5-E5C5-47AA-8FB2-ABBFBE69B251}">
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="45.453125" customWidth="1"/>
     <col min="15" max="15" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:22" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
@@ -848,8 +855,11 @@
       <c r="U1" s="26" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="V1" s="35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="32" t="s">
         <v>13</v>
       </c>
@@ -913,8 +923,11 @@
       <c r="U2" s="33">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="V2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="32" t="s">
         <v>14</v>
       </c>
@@ -978,8 +991,11 @@
       <c r="U3" s="33">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="V3" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="32" t="s">
         <v>15</v>
       </c>
@@ -1043,8 +1059,11 @@
       <c r="U4" s="33">
         <v>53</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="V4" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" s="32" t="s">
         <v>16</v>
       </c>
@@ -1108,8 +1127,11 @@
       <c r="U5" s="33">
         <v>44</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="V5" s="36">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="32" t="s">
         <v>17</v>
       </c>
@@ -1173,8 +1195,11 @@
       <c r="U6" s="33">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="V6" s="36">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="32" t="s">
         <v>18</v>
       </c>
@@ -1238,8 +1263,11 @@
       <c r="U7" s="33">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="V7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" s="32" t="s">
         <v>19</v>
       </c>
@@ -1303,8 +1331,11 @@
       <c r="U8" s="33">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="V8" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" s="32" t="s">
         <v>47</v>
       </c>
@@ -1368,8 +1399,11 @@
       <c r="U9" s="33">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" ht="29" x14ac:dyDescent="0.35">
+      <c r="V9" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="32" t="s">
         <v>20</v>
       </c>
@@ -1433,20 +1467,23 @@
       <c r="U10" s="33">
         <v>49</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="V10" s="37">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" s="31"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="32"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" s="32"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" s="32"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" s="32"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
@@ -1472,14 +1509,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1C073F-9039-4462-B525-9698BD783580}">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="42.81640625" customWidth="1"/>
     <col min="2" max="2" width="13.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
@@ -1534,8 +1571,11 @@
       <c r="R1" s="27" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="16" x14ac:dyDescent="0.4">
+      <c r="S1" s="38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
@@ -1590,8 +1630,11 @@
       <c r="R2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+      <c r="S2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="32" t="s">
         <v>20</v>
       </c>
@@ -1646,8 +1689,11 @@
       <c r="R3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="32" t="s">
         <v>14</v>
       </c>
@@ -1702,8 +1748,11 @@
       <c r="R4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="32" t="s">
         <v>15</v>
       </c>
@@ -1758,8 +1807,11 @@
       <c r="R5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="32" t="s">
         <v>16</v>
       </c>
@@ -1814,8 +1866,11 @@
       <c r="R6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -1862,8 +1917,11 @@
       <c r="R7">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -1918,8 +1976,11 @@
       <c r="R8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="32" t="s">
         <v>19</v>
       </c>
@@ -1974,25 +2035,28 @@
       <c r="R9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="32" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="31"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="32"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" s="32"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" s="32"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="32"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
@@ -2018,7 +2082,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12EEDAFB-5DD9-4712-8169-3CA90A65D01B}">
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="41.453125" bestFit="1" customWidth="1"/>
@@ -2028,7 +2092,7 @@
     <col min="10" max="10" width="7.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2083,8 +2147,11 @@
       <c r="R1" s="28" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="16" x14ac:dyDescent="0.4">
+      <c r="S1" s="39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
@@ -2139,8 +2206,11 @@
       <c r="R2" s="28">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+      <c r="S2" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>20</v>
       </c>
@@ -2189,8 +2259,11 @@
       <c r="R3" s="28">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S3" s="28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -2245,8 +2318,11 @@
       <c r="R4" s="28">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="S4" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -2299,8 +2375,11 @@
       <c r="R5" s="11" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S5" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -2355,8 +2434,11 @@
       <c r="R6" s="34">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S6" s="34">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -2411,8 +2493,11 @@
       <c r="R7" s="34">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S7" s="34">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -2451,8 +2536,11 @@
       <c r="R8" s="28">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S8" s="28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -2507,8 +2595,11 @@
       <c r="R9" s="34">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S9" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>47</v>
       </c>
@@ -2540,8 +2631,11 @@
       <c r="R10" s="28">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S10" s="28">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="K13" s="10"/>
     </row>
   </sheetData>
@@ -2785,6 +2879,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006CDDA926EB07344AB32891125AAEC5BC" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90892fbecef2bc118e048677eec85496">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="84e45b98-9724-46df-936f-ec42a4cf951b" xmlns:ns4="6d0ea381-1626-4603-a356-2e0ae14a7169" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd11a616b5a0cf6b6198f2be1ebf2a7a" ns3:_="" ns4:_="">
     <xsd:import namespace="84e45b98-9724-46df-936f-ec42a4cf951b"/>
@@ -3037,15 +3140,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29346A3B-E74B-4386-AD79-218823B89808}">
   <ds:schemaRefs>
@@ -3057,6 +3151,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{402FBE93-6AD6-436A-9711-D8E18344BF8D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBDD83E4-3402-43C9-9418-378586538C46}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3073,12 +3175,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{402FBE93-6AD6-436A-9711-D8E18344BF8D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>